--- a/EPIC_0011_Profile_Management.xlsx
+++ b/EPIC_0011_Profile_Management.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C89D2AA-5635-47D5-BB2D-9909DFE1350C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3999BFC-1B47-4340-B86B-3463266FDD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserDriverWebIntialilzer" sheetId="43" r:id="rId1"/>
@@ -312,9 +312,6 @@
   </si>
   <si>
     <t>TC_HY_06_Customer_Language_Check</t>
-  </si>
-  <si>
-    <t>TC_RG_06_Customer_Language_Check</t>
   </si>
   <si>
     <t>This comprehensive, cross-platform regression test suite validates the customer onboarding lifecycle, profile verification, and dynamic UI localization capabilities across both native mobile environments and the centralized web admin portal. The script begins by orchestrating an initial mobile registration and OTP verification sequence, shifts context to the web portal to escalate the profile from the Non-Verified Customers grid to the Verified Customers list via metadata injection and profile image uploads, and logs back into the mobile app to verify access. It then comprehensively audits the localization subsystem by performing sequential runtime dialect switches—transitioning the interface dynamically from English to Tamil, Tamil to Hindi, and back to English—while verifying that language save triggers update the UI element bounds properly without memory leaks. Finally, the suite executes a clean teardown flow by triggering a native Delete Account action from the mobile settings drawer and cross-verifying that the profile records are accurately reassigned to the web admin's Deleted Customers master repository.</t>
@@ -596,9 +593,6 @@
     <t>TC_HY_07_Driver_Language_Check</t>
   </si>
   <si>
-    <t>TC_RG_07_Driver_Language_Check</t>
-  </si>
-  <si>
     <t>This end-to-end, cross-platform regression test suite orchestrates a complex testing lifecycle for driver management by coordinating operations between the central web administration portal and native mobile driver application runtimes. The execution flow begins by initializing clean device environments using the reload_app keyword and shifts context to the web portal to register a new driver profile with comprehensive metadata mapping—including automated profile picture uploads, customized vehicle specifications ("Pink Auto"), and corporate banking infrastructure parameters. The test then executes a multi-tiered regulatory validation pipeline by locating the profile in the Pending Documents grid, uploading a simulated driving license file with an active expiry date, and escalating the profile to the official Approved Drivers registry. Transitioning into the native mobile engine environment, the suite authenticates the newly approved driver using dynamic OTP routing, processes specialized compliance checkboxes, and thoroughly audits the application's localization subsystem by executing dynamic runtime language shifts—transitioning the interface seamlessly from English to Tamil, Tamil to Hindi, and back to English. Finally, the suite tests legal compliance and lifecycle termination rules by triggering a native Delete Account flow from the driver app interface and verifying that the record instantly relocates to the web admin's Deleted Drivers repository under localized filtering conditions.</t>
   </si>
   <si>
@@ -857,6 +851,12 @@
 119.Wait For Load,wait,1000,
 120. Enter Driver Name,type,{autoName},"admin.drivers.name_filter.input" 
 121.Wait For Load,wait,3000,</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Customer_Language_Check</t>
+  </si>
+  <si>
+    <t>TC_RG_03_Driver_Language_Check</t>
   </si>
 </sst>
 </file>
@@ -1357,25 +1357,25 @@
         <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1447,31 +1447,31 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J2" s="2"/>
     </row>
